--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -606,11 +606,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ly enoughâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L74: symbol-only separator/garbage line :: 1850.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: I</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: %</t>
+          <t>L27: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -712,7 +716,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: -</t>
+          <t>L29: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -755,7 +759,7 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: /</t>
+          <t>L35: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -798,7 +802,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L80: symbol-only separator/garbage line :: 1850.</t>
+          <t>L42: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -841,7 +845,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: +</t>
+          <t>L80: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -884,7 +888,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: /</t>
+          <t>L83: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -927,7 +931,7 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 9</t>
+          <t>L85: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -968,7 +972,11 @@
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L102: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -993,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1032,7 +1040,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
